--- a/IndentMe_new_indented.xlsx
+++ b/IndentMe_new_indented.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jamasoftware-my.sharepoint.com/personal/pknowles_jamasoftware_com/Documents/Documents/Coding/Excel-Indent-Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD370524077F312F2563088B35299F4B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AE38F27-8A68-4298-87E0-D333DC64057E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_085D462F135A5A4FE00358175DA10EFD902D8469" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="18210" windowHeight="12405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Heading</t>
   </si>
@@ -40,49 +40,31 @@
     <t>1. Title</t>
   </si>
   <si>
-    <t xml:space="preserve">    1.1 Subtitle</t>
-  </si>
-  <si>
     <t>1.1 Subtitle</t>
   </si>
   <si>
-    <t xml:space="preserve">        1.1.1 Sub-Subtitle</t>
+    <t>1.1.1 Sub-Subtitle</t>
   </si>
   <si>
     <t>1.1.1</t>
   </si>
   <si>
-    <t>1.1.1 Sub-Subtitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            Requirement Text</t>
+    <t>Requirement Text</t>
   </si>
   <si>
     <t>1.1.1.1</t>
   </si>
   <si>
-    <t>Requirement Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        1.1.2 Sub-Subtitle</t>
+    <t>1.1.2 Sub-Subtitle</t>
   </si>
   <si>
     <t>1.1.2</t>
   </si>
   <si>
-    <t>1.1.2 Sub-Subtitle</t>
-  </si>
-  <si>
     <t>1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">    1.2 Subtitle</t>
-  </si>
-  <si>
     <t>1.2 Subtitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Requirement Text</t>
   </si>
   <si>
     <t>1.2.1</t>
@@ -141,10 +123,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,9 +441,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -489,7 +477,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3">
@@ -499,83 +487,83 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
+      <c r="A5" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
+      <c r="A6" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
+      <c r="A7" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
+      <c r="A8" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B8">
         <v>1.2</v>
@@ -584,24 +572,24 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
+      <c r="A9" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>2</v>
